--- a/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:30:34+00:00</t>
+    <t>2026-06-16T13:53:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T13:53:28+00:00</t>
+    <t>2026-06-16T14:51:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:51:07+00:00</t>
+    <t>2026-06-17T12:15:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T12:15:06+00:00</t>
+    <t>2026-06-17T13:49:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T13:49:22+00:00</t>
+    <t>2026-06-17T15:07:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T15:07:59+00:00</t>
+    <t>2026-06-17T15:48:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T15:48:42+00:00</t>
+    <t>2026-06-18T10:03:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T10:03:06+00:00</t>
+    <t>2026-06-18T13:10:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:10:23+00:00</t>
+    <t>2026-06-18T14:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:01:22+00:00</t>
+    <t>2026-06-22T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -569,7 +569,7 @@
 </t>
   </si>
   <si>
-    <t>Référence vers une Observation représentant la difficulté</t>
+    <t>Difficulté de l'acte</t>
   </si>
   <si>
     <t>Extension permettant d'indiquer la difficulté perçue ou mesurée d'un acte.</t>
@@ -693,11 +693,11 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-medication-administration-document)
+    <t xml:space="preserve">Reference(Observation|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-medication-administration-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-procedure-document)
 </t>
   </si>
   <si>
-    <t>Observation de score ou administration de médicament associée à l'acte (ex. : produit administré lors d'un acte d'imagerie).</t>
+    <t>Événement associé : score (Cormack ou ASA), administration de médicament ou procédure associée à l’acte (ex. produit administré lors d’un acte d’imagerie).</t>
   </si>
   <si>
     <t>A larger event of which this particular procedure is a component or step.</t>
@@ -872,7 +872,7 @@
 </t>
   </si>
   <si>
-    <t>Circonstances ayant décidé de l'acte</t>
+    <t>Rencontre associée à l'acte</t>
   </si>
   <si>
     <t>The Encounter during which this Procedure was created or performed or to which the creation of this record is tightly associated.</t>
@@ -1878,7 +1878,7 @@
     <t>Procedure.usedReference</t>
   </si>
   <si>
-    <t>Réference interne à un DM</t>
+    <t>Réference à un DM</t>
   </si>
   <si>
     <t>Identifies medications, devices and any other substance used as part of the procedure.</t>

--- a/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:03:44+00:00</t>
+    <t>2026-06-22T08:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:16:05+00:00</t>
+    <t>2026-06-22T09:23:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:23:37+00:00</t>
+    <t>2026-06-22T09:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
